--- a/naver-place-crawler/results_health/사하구_PT.xlsx
+++ b/naver-place-crawler/results_health/사하구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐크래커 부산점</t>
+          <t>호이스트짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymcracker1517@naver.com</t>
+          <t>himallos@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>051-293-8788</t>
+          <t>051-204-1754</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 365 가락타운1단지 145동 상가 3F</t>
+          <t>부산광역시 사하구 하신번영로 310 2층 호이스트짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymcracker1517</t>
+          <t>https://blog.naver.com/himallos</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="R2" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1213321291</t>
+          <t>37281927</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213321291</t>
+          <t>https://m.place.naver.com/place/37281927</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리얼바디 기구필라테스&amp;PT</t>
+          <t>휘트니스베이직</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>realbodypt@naver.com</t>
+          <t>ryounghwa@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-992-5252</t>
+          <t>051-204-5556</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다송로72번길 55 동양빌딩 5층</t>
+          <t>부산광역시 사하구 낙동대로 184 동은빌딩 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/realbody_pilates</t>
+          <t>https://open.kakao.com/o/swxfwIHe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38530720</t>
+          <t>36448996</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38530720</t>
+          <t>https://m.place.naver.com/place/36448996</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -834,41 +834,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>하파휘트니스</t>
+          <t>블루밍PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kdh31307o@naver.com</t>
+          <t>blooming_pt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>051-293-3000</t>
+          <t>051-262-0232</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 474 대하빌딩 7층</t>
+          <t>부산광역시 사하구 다대낙조1길 11 3층 블루밍PT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/blooming_pt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>302</v>
+        <v>112</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>329</v>
       </c>
       <c r="R5" t="n">
-        <v>334</v>
+        <v>441</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>36771036</t>
+          <t>1231432652</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36771036</t>
+          <t>https://m.place.naver.com/place/1231432652</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 트렌드핏 피트니스 하단점</t>
+          <t>지존 헬스&amp;피트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gkeks66@naver.com</t>
+          <t>zzonept@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1303-2924</t>
+          <t>051-266-2660</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 475 2층</t>
+          <t>부산광역시 사하구 다대로 207 세정아울렛 1,2,3층 (상담은 3층 카운터)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gkeks66</t>
+          <t>https://blog.naver.com/zzonept</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1547</v>
+        <v>161</v>
       </c>
       <c r="Q6" t="n">
-        <v>535</v>
+        <v>93</v>
       </c>
       <c r="R6" t="n">
-        <v>2082</v>
+        <v>254</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,52 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1354278156</t>
+          <t>38563721</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354278156</t>
+          <t>https://m.place.naver.com/place/38563721</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>프라이빗GYM</t>
+          <t>갓바디휘트니스 당리점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>privategym2014@naver.com</t>
+          <t>tjdgns3591@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>051-203-3190</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 388 경성리치W상가 3층</t>
+          <t>부산광역시 사하구 낙동대로 410 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/privategym2014</t>
+          <t>https://open.kakao.com/o/sDJqNLIh</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,22 +1078,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36132952</t>
+          <t>1003392887</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36132952</t>
+          <t>https://m.place.naver.com/place/1003392887</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>블루밍PT</t>
+          <t>괴정메가스포츠센터&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>blooming_pt@naver.com</t>
+          <t>bbvn1539@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>051-262-0232</t>
+          <t>051-207-7744</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대낙조1길 11 3층 블루밍PT</t>
+          <t>부산광역시 사하구 낙동대로 261 자유상가 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blooming_pt</t>
+          <t>https://blog.naver.com/bbvn1539</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>328</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1231432652</t>
+          <t>16619186</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231432652</t>
+          <t>https://m.place.naver.com/place/16619186</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>워너짐헬스&amp;PT 하단2지점</t>
+          <t>라인피티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wannagym87@naver.com</t>
+          <t>linerkacjs@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1413-8976</t>
+          <t>0507-1334-6965</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신중앙로 299 3층</t>
+          <t>부산광역시 사하구 감천로 46 3층 라인피티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wannagym87/223954977011</t>
+          <t>https://blog.naver.com/linerkacjs</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>304</v>
       </c>
       <c r="R9" t="n">
-        <v>69</v>
+        <v>401</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,34 +1290,34 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1154806768</t>
+          <t>1142205137</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154806768</t>
+          <t>https://m.place.naver.com/place/1142205137</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>글쓰기,독서지도</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>써밋퍼스널트레이닝</t>
+          <t>피티독서학습학원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jjuyaa_a@naver.com</t>
+          <t>giveapeck@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1329,7 +1325,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 제석로 160 당리동1차 동원베네스트 아파트 상가</t>
+          <t>부산광역시 사하구 동매로 167 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1369,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1380,47 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1515008554</t>
+          <t>1213403738</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1515008554</t>
+          <t>https://m.place.naver.com/place/1213403738</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>올짐 피트니스 &amp; 사우나 대티점</t>
+          <t>제이엠핏 하단본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allgym_daeti@naver.com</t>
+          <t>sf9669@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1384-8306</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 137 대티역 스마트W 상가 1층 올짐 휘트니스 &amp; 사우나</t>
+          <t>부산광역시 사하구 낙동대로516번길 56 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allgym_daeti</t>
+          <t>https://blog.naver.com/sf9669</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,17 +1451,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>292</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>691</v>
+        <v>45</v>
       </c>
       <c r="R11" t="n">
-        <v>983</v>
+        <v>52</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1698150913</t>
+          <t>36259188</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698150913</t>
+          <t>https://m.place.naver.com/place/36259188</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1492,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더머슬짐 신평점 헬스&amp;PT</t>
+          <t>레드핏 퍼스널트레이닝 스튜디오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yongin8929@naver.com</t>
+          <t>baby3258@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1465-6464</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 307 4층</t>
+          <t>부산광역시 사하구 낙동대로 393 사하구청 건너편 버스정류소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yongin8929</t>
+          <t>https://blog.naver.com/baby3258</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,17 +1541,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>460</v>
+        <v>36</v>
       </c>
       <c r="R12" t="n">
-        <v>554</v>
+        <v>49</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,51 +1560,47 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1425619781</t>
+          <t>33907135</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1425619781</t>
+          <t>https://m.place.naver.com/place/33907135</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO피트니스&amp;대기구필라테스 괴정점</t>
+          <t>블로썸핏 하단 PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gofitness_gj@naver.com</t>
+          <t>blossomfit@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1402-0240</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로 200 형지스퀘어 빌딩 7층, 8층</t>
+          <t>부산광역시 사하구 낙동대로 491 7층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gofit_goejeong/</t>
+          <t>https://blog.naver.com/blossomfit</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1642,7 +1626,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1651,13 +1635,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="Q13" t="n">
-        <v>451</v>
+        <v>1184</v>
       </c>
       <c r="R13" t="n">
-        <v>691</v>
+        <v>1349</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,34 +1650,34 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>31681303</t>
+          <t>1221239515</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31681303</t>
+          <t>https://m.place.naver.com/place/1221239515</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>슬기로운 운동생활</t>
+          <t>허그짐 다대포 낫개점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>wfl201911@naver.com</t>
+          <t>huggymdadaepo9704@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1701,12 +1685,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다송로68번길 10</t>
+          <t>부산광역시 사하구 다송로84번길 52 2, 3층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/huggymdadaepo9704</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,12 +1700,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1737,17 +1721,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>385</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>347</v>
       </c>
       <c r="R14" t="n">
-        <v>16</v>
+        <v>732</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,51 +1740,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13144603</t>
+          <t>1095357843</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13144603</t>
+          <t>https://m.place.naver.com/place/1095357843</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>클리어짐</t>
+          <t>메디앤컬필라테스  하단점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>clear_gym@naver.com</t>
+          <t>uinawe@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1352-4221</t>
+          <t>0507-1338-3340</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로233번길 21-17</t>
+          <t>부산광역시 사하구 낙동남로 1414 8층 메디앤컬필라테스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/clear_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,12 +1794,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,17 +1815,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>70</v>
+        <v>609</v>
       </c>
       <c r="Q15" t="n">
-        <v>103</v>
+        <v>324</v>
       </c>
       <c r="R15" t="n">
-        <v>173</v>
+        <v>933</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1545911961</t>
+          <t>1202193535</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545911961</t>
+          <t>https://m.place.naver.com/place/1202193535</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1872,34 +1856,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>스마트w 사우나&amp;휘트니스</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wfitness3@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1363-0214</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장림번영로104번길 10 지하1층 W사우나&amp;휘트니스</t>
+          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wfitness3</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1909,7 +1893,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1925,17 +1909,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>430</v>
       </c>
       <c r="R16" t="n">
-        <v>50</v>
+        <v>1585</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,51 +1928,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1038609556</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038609556</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>인더필라테스 &amp; 요가 괴정점</t>
+          <t>헬스보이짐 하단점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>inthepila@naver.com</t>
+          <t>healthboy34@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1371-1120</t>
+          <t>0507-1489-5775</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로186번길 6 5,6층(괴정동, 하정빌딩)</t>
+          <t>부산광역시 사하구 낙동남로 1403 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym01</t>
+          <t>https://blog.naver.com/healthboy34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2003,7 +1987,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>79</v>
+        <v>587</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>632</v>
       </c>
       <c r="R17" t="n">
-        <v>104</v>
+        <v>1219</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1314348239</t>
+          <t>1791255308</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314348239</t>
+          <t>https://m.place.naver.com/place/1791255308</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2044,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>디파인짐 구평점</t>
+          <t>슬릭부스트 괴정점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>thefinegym_gp@naver.com</t>
+          <t>sleekboost_goejeong@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1433-7073</t>
+          <t>0507-1319-3027</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 서포로30번길 3 3층 301,302호</t>
+          <t>부산광역시 사하구 낙동대로 203 209, 210A호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thefinegym</t>
+          <t>https://www.instagram.com/sleekboost_goejeong</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2108,7 +2092,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q18" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="R18" t="n">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,56 +2116,56 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1008480964</t>
+          <t>1975216862</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008480964</t>
+          <t>https://m.place.naver.com/place/1975216862</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>지음 필라테스&amp;PT</t>
+          <t>더케이피트니스 롯데마트사하</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jieumpilates@naver.com</t>
+          <t>thekfitness@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1423-7719</t>
+          <t>0507-1334-1844</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 630 4층</t>
+          <t>부산광역시 사하구 을숙도대로 610 롯데마트 사하점 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jieum_pilates</t>
+          <t>https://www.instagram.com/the.k_fitness_saha</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2191,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>318</v>
       </c>
       <c r="R19" t="n">
-        <v>140</v>
+        <v>482</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1782696469</t>
+          <t>1183759558</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782696469</t>
+          <t>https://m.place.naver.com/place/1183759558</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2248,29 +2232,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
+          <t>제이엘피트니스 신평점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jlfitness_j@naver.com</t>
+          <t>barbell_bbbccc@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1310-1470</t>
+          <t>0507-1326-6105</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장림번영로 50 상가 2층</t>
+          <t>부산광역시 사하구 하신중앙로 180 신익상가 지하 11호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
+          <t>https://blog.naver.com/barbell_bbbccc</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,7 +2269,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,13 +2289,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1195</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>615</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>1810</v>
+        <v>33</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,51 +2304,47 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1315960121</t>
+          <t>1099405868</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315960121</t>
+          <t>https://m.place.naver.com/place/1099405868</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>지존 헬스&amp;피트니스</t>
+          <t>슬기로운 운동생활</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>zzonept@naver.com</t>
+          <t>wfl201911@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>051-266-2660</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 207 세정아울렛 1,2,3층 (상담은 3층 카운터)</t>
+          <t>부산광역시 사하구 다송로68번길 10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zzonept</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2374,12 +2354,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2399,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,51 +2394,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38563721</t>
+          <t>13144603</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38563721</t>
+          <t>https://m.place.naver.com/place/13144603</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>레드 피트니스</t>
+          <t>더머슬짐 신평점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>moonsi870@naver.com</t>
+          <t>yongin8929@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1354-0550</t>
+          <t>0507-1465-6464</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 제석로 89 3층, 4층 레드피트니스</t>
+          <t>부산광역시 사하구 장평로 307 4층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/red_fitness25</t>
+          <t>https://blog.naver.com/yongin8929</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2473,7 +2453,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2493,13 +2473,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="R22" t="n">
-        <v>380</v>
+        <v>554</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,51 +2488,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1003594161</t>
+          <t>1425619781</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003594161</t>
+          <t>https://m.place.naver.com/place/1425619781</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>최귀성프로짐</t>
+          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>umsoso@naver.com</t>
+          <t>inthegym01@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1375-4667</t>
+          <t>0507-1358-6699</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 299 3층 최귀성프로짐</t>
+          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/umsoso</t>
+          <t>https://blog.naver.com/inthegym01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2587,13 +2567,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>201</v>
+        <v>597</v>
       </c>
       <c r="Q23" t="n">
-        <v>167</v>
+        <v>719</v>
       </c>
       <c r="R23" t="n">
-        <v>368</v>
+        <v>1316</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,47 +2582,51 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1650411626</t>
+          <t>1419272513</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650411626</t>
+          <t>https://m.place.naver.com/place/1419272513</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>글쓰기,독서지도</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>피티독서학습학원</t>
+          <t>피트니스 넘버원 헬스&amp;PT 괴정점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>realpt0108@naver.com</t>
+          <t>fitnessgymseung@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1388-7941</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 동매로 167 4층</t>
+          <t>부산광역시 사하구 낙동대로 203 엔스타상가 210,211호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://open.kakao.com/me/gymseung</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2652,7 +2636,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2668,22 +2652,22 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>318</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,47 +2676,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1213403738</t>
+          <t>1519532322</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213403738</t>
+          <t>https://m.place.naver.com/place/1519532322</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제이엠핏 하단본점</t>
+          <t>404피트니스 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sf9669@naver.com</t>
+          <t>404fitnesshadan@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1395-4026</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로516번길 56 6층</t>
+          <t>부산광역시 사하구 낙동대로 487 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sf9669</t>
+          <t>https://www.instagram.com/404_fitness_hadan/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2747,7 +2735,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2758,22 +2746,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>419</v>
       </c>
       <c r="Q25" t="n">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="R25" t="n">
-        <v>52</v>
+        <v>708</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,51 +2770,47 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36259188</t>
+          <t>1669341529</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36259188</t>
+          <t>https://m.place.naver.com/place/1669341529</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>바디로운필라테스 하단점</t>
+          <t>점핑홀릭</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bodyroun3@naver.com</t>
+          <t>llbonobono@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1488-1037</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1423 태영빌딩 4층</t>
+          <t>부산광역시 사하구 장평로 441 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://bodyrounpilates.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2836,7 +2820,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2857,17 +2841,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>196</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>616</v>
+        <v>11</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2860,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1859898786</t>
+          <t>1051113737</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1859898786</t>
+          <t>https://m.place.naver.com/place/1051113737</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2882,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>폴인기구필라테스&amp;웨이트PT 부산 하단점</t>
+          <t>바디로운필라테스 하단점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fallin__22@naver.com</t>
+          <t>bodyroun3@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1423-8311</t>
+          <t>0507-1488-1037</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로516번길 56 캠퍼스프라자2층 204호</t>
+          <t>부산광역시 사하구 낙동남로 1423 태영빌딩 4층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fallin__22</t>
+          <t>https://bodyrounpilates.com</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2935,7 +2919,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2955,13 +2939,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>141</v>
+        <v>425</v>
       </c>
       <c r="Q27" t="n">
-        <v>495</v>
+        <v>197</v>
       </c>
       <c r="R27" t="n">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,51 +2954,51 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>548118354</t>
+          <t>1859898786</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548118354</t>
+          <t>https://m.place.naver.com/place/1859898786</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>헬스보이짐 하단점 PT&amp;헬스</t>
+          <t>바디팩토리 당리점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>healthboy34@naver.com</t>
+          <t>skadn107@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1489-5775</t>
+          <t>0507-1383-9688</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1403 2층</t>
+          <t>부산광역시 사하구 괴정로 99 다온빌딩 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy34</t>
+          <t>https://blog.naver.com/skadn107</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3049,13 +3033,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>586</v>
+        <v>93</v>
       </c>
       <c r="Q28" t="n">
-        <v>629</v>
+        <v>77</v>
       </c>
       <c r="R28" t="n">
-        <v>1215</v>
+        <v>170</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3048,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1791255308</t>
+          <t>1077347457</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791255308</t>
+          <t>https://m.place.naver.com/place/1077347457</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3070,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>제이엘피트니스 신평점</t>
+          <t>준헬스피티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>barbell_bbbccc@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1326-6105</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신중앙로 180 신익상가 지하 11호</t>
+          <t>부산광역시 사하구 감천로 60-1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbell_bbbccc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3118,12 +3098,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3139,17 +3119,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,51 +3138,51 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1099405868</t>
+          <t>1027715181</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099405868</t>
+          <t>https://m.place.naver.com/place/1027715181</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>슬릭부스트 괴정점</t>
+          <t>EMS트레이닝</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sleekboost_goejeong@naver.com</t>
+          <t>emskoreasje@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1319-3027</t>
+          <t>051-204-9901</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 203 209, 210A호</t>
+          <t>부산광역시 사하구 하신번영로 385 SM빌딩 3층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sleekboost_goejeong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3212,7 +3192,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3233,17 +3213,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,51 +3232,51 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1975216862</t>
+          <t>36929012</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975216862</t>
+          <t>https://m.place.naver.com/place/36929012</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>부속시설</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>호이스트짐</t>
+          <t>지존헬스 &amp; 지존GX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>himallos@naver.com</t>
+          <t>yeo_and_sook@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>051-204-1754</t>
+          <t>0507-1429-9525</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 310 2층 호이스트짐</t>
+          <t>부산광역시 사하구 다대로 207 1,2,3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/himallos</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3306,12 +3286,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3327,17 +3307,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="Q31" t="n">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3326,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>37281927</t>
+          <t>1135097164</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37281927</t>
+          <t>https://m.place.naver.com/place/1135097164</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3368,44 +3348,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>오케이피트니스 다대포점 헬스&amp;PT</t>
+          <t>다대포헬스 &amp; PT 아이언짐 4호점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>okfitness_dadaepo@naver.com</t>
+          <t>rlaruddjs1109@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1342-9583</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대낙조1길 5 . 3,4층</t>
+          <t>부산광역시 사하구 다대로 473 맘모스상가 4층 아이언짐</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.okfitness.co.kr</t>
+          <t>https://www.instagram.com/irongym_dadaepo_2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3416,7 +3392,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3425,13 +3401,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>156</v>
+        <v>451</v>
       </c>
       <c r="Q32" t="n">
-        <v>167</v>
+        <v>392</v>
       </c>
       <c r="R32" t="n">
-        <v>323</v>
+        <v>843</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,51 +3416,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1999206798</t>
+          <t>1051347619</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999206798</t>
+          <t>https://m.place.naver.com/place/1051347619</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>스핀업스피닝</t>
+          <t>핏튜브짐 &amp; 필라테스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kej6254@naver.com</t>
+          <t>boong_see@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1400-2070</t>
+          <t>0507-1465-5152</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 548</t>
+          <t>부산광역시 사하구 하신번영로 417 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/spinupspining</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3494,12 +3470,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3519,13 +3495,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,51 +3510,51 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>37333233</t>
+          <t>1226166767</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37333233</t>
+          <t>https://m.place.naver.com/place/1226166767</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>라인피티</t>
+          <t>네오피트니스 다대점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>linerkacjs@naver.com</t>
+          <t>lkz2995@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1334-6965</t>
+          <t>0507-1424-8531</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 감천로 46 3층 라인피티</t>
+          <t>부산광역시 사하구 다대로 613 자유마트상가 5층 502호 네오피트니스</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/linerkacjs</t>
+          <t>https://blog.naver.com/lkz2995</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3613,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="n">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="R34" t="n">
-        <v>401</v>
+        <v>198</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,51 +3604,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1142205137</t>
+          <t>1337361253</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142205137</t>
+          <t>https://m.place.naver.com/place/1337361253</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>부속시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>지존헬스 &amp; 지존GX</t>
+          <t>곤코치피트니스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>yeo_and_sook@naver.com</t>
+          <t>groupcircuit@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1429-9525</t>
+          <t>0507-1348-7871</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 207 1,2,3층</t>
+          <t>부산광역시 사하구 낙동대로 524 지하층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/groupcircuit</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,12 +3658,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3707,13 +3683,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R35" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3698,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1135097164</t>
+          <t>1173727453</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135097164</t>
+          <t>https://m.place.naver.com/place/1173727453</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3744,29 +3720,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오앤오짐 장림</t>
+          <t>플러스짐 / 플러스휘트니스 헬스&amp;PT 다대포점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mmsy6242@naver.com</t>
+          <t>plusfitnessdadae@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1383-1354</t>
+          <t>0507-1384-8809</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신중앙로 21 2층</t>
+          <t>부산광역시 사하구 다대낙조2길 3 2층 201호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ono_pt_grit</t>
+          <t>https://blog.naver.com/plusfitnessdadae</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3781,7 +3757,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3797,17 +3773,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="R36" t="n">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,51 +3792,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1355627213</t>
+          <t>1260784487</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355627213</t>
+          <t>https://m.place.naver.com/place/1260784487</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>림필라테스&amp;PT스튜디오</t>
+          <t>아돌프그룹PT 다대포점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>lipblossom@naver.com</t>
+          <t>adolph_dadaepo@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1419-8402</t>
+          <t>0507-1458-0265</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신중앙로313번길 54 3층</t>
+          <t>부산광역시 사하구 다대로 613 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rimpilates_pt</t>
+          <t>https://blog.naver.com/adolph_dadaepo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3875,7 +3851,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3895,13 +3871,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="R37" t="n">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,51 +3886,51 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1704290562</t>
+          <t>1159008518</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704290562</t>
+          <t>https://m.place.naver.com/place/1159008518</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>하단pt 더원짐</t>
+          <t>다대포 리핏1대1바디스쿨</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jlove518@naver.com</t>
+          <t>sondh44@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1411-0656</t>
+          <t>0507-1424-0777</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 381-4 2층 더원짐</t>
+          <t>부산광역시 사하구 다대로 547 윤영빌딩 7층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jlove518</t>
+          <t>https://blog.naver.com/sondh44</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3980,7 +3956,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3989,13 +3965,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="R38" t="n">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,51 +3980,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>53386360</t>
+          <t>33252149</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/53386360</t>
+          <t>https://m.place.naver.com/place/33252149</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스  하단점</t>
+          <t>스카이PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rkfql88@naver.com</t>
+          <t>deok51@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1338-3340</t>
+          <t>0507-1300-6238</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1414 8층 메디앤컬필라테스</t>
+          <t>부산광역시 사하구 다대낙조1길 19 성호빌딩 6층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/deok51</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4058,12 +4034,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4083,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>607</v>
+        <v>97</v>
       </c>
       <c r="Q39" t="n">
-        <v>323</v>
+        <v>101</v>
       </c>
       <c r="R39" t="n">
-        <v>930</v>
+        <v>198</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1202193535</t>
+          <t>1953925821</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202193535</t>
+          <t>https://m.place.naver.com/place/1953925821</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4120,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>위더스짐</t>
+          <t>24시 트렌드핏 피트니스 하단점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>with_us_1225@naver.com</t>
+          <t>gkeks66@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1303-4471</t>
+          <t>0507-1303-2924</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 519 지하 1층 위더스짐</t>
+          <t>부산광역시 사하구 낙동대로 475 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/with_us_1225</t>
+          <t>https://blog.naver.com/gkeks66</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4177,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>65</v>
+        <v>1552</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="R40" t="n">
-        <v>84</v>
+        <v>2032</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4192,51 +4168,51 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1081043765</t>
+          <t>1354278156</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081043765</t>
+          <t>https://m.place.naver.com/place/1354278156</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>메이크핏</t>
+          <t>요가인</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>make___fit@naver.com</t>
+          <t>bypoleon@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1309-2919</t>
+          <t>051-205-3114</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 239 2층</t>
+          <t>부산광역시 사하구 낙동대로 267 신동양상가 3층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/make___fit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4246,12 +4222,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,17 +4243,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,47 +4262,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1364930930</t>
+          <t>1258904158</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364930930</t>
+          <t>https://m.place.naver.com/place/1258904158</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>블로썸핏 하단 PT</t>
+          <t>그린피트니스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>blossomfit@naver.com</t>
+          <t>hcy1507@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>051-208-0551</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 491 7층</t>
+          <t>부산광역시 사하구 하신번영로201번길 20 3층4층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blossomfit</t>
+          <t>https://www.instagram.com/2019__gf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4341,7 +4321,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4361,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1180</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1344</v>
+        <v>6</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,51 +4356,51 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1221239515</t>
+          <t>1088337947</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221239515</t>
+          <t>https://m.place.naver.com/place/1088337947</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>바디팩토리 당리점</t>
+          <t>아이콘휘트니스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>skadn107@naver.com</t>
+          <t>spain0805@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1383-9688</t>
+          <t>051-206-9996</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 괴정로 99 다온빌딩 3층</t>
+          <t>부산광역시 사하구 낙동남로 1422 청경빌딩 6층 아이콘 휘트니스</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skadn107</t>
+          <t>https://www.instagram.com/icon_busan</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4435,7 +4415,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4455,13 +4435,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="Q43" t="n">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="R43" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4470,51 +4450,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1077347457</t>
+          <t>37379330</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077347457</t>
+          <t>https://m.place.naver.com/place/37379330</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아돌프그룹PT 다대포점</t>
+          <t>머슬팩토리 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>adolph_dadaepo@naver.com</t>
+          <t>musclefactory_hadan@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1458-0265</t>
+          <t>0507-1372-0206</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 613 2층</t>
+          <t>부산광역시 사하구 하신번영로201번길 10 지하1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/adolph_dadaepo</t>
+          <t>https://blog.naver.com/musclefactory_hadan</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4549,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="Q44" t="n">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="R44" t="n">
-        <v>134</v>
+        <v>259</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1159008518</t>
+          <t>1846192246</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159008518</t>
+          <t>https://m.place.naver.com/place/1846192246</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4566,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>트레이닝스튜디오 바름 본점</t>
+          <t>피지오컨디셔닝운동센터</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>yourim03070@naver.com</t>
+          <t>move_tai@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1433-9887</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 381 도원 소아과3층</t>
+          <t>부산광역시 사하구 낙동대로 137 103동 2층 피지오컨디셔닝운동센터</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@피지오클럽</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4618,7 +4594,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4639,17 +4615,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,51 +4634,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>905213182</t>
+          <t>1452522646</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/905213182</t>
+          <t>https://m.place.naver.com/place/1452522646</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동아기능성운동트레이닝센터</t>
+          <t>코치엔짐</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dfet0226@naver.com</t>
+          <t>iron0377@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1494-7910</t>
+          <t>0507-1386-9682</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로550번길 37 예술체육대학1관 106호</t>
+          <t>부산광역시 사하구 다송로72번길 80 라브랜드 4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dfet0226</t>
+          <t>https://blog.naver.com/iron0377</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4737,13 +4713,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>161</v>
+        <v>546</v>
       </c>
       <c r="Q46" t="n">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="R46" t="n">
-        <v>458</v>
+        <v>744</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4728,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1619665911</t>
+          <t>1524946927</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619665911</t>
+          <t>https://m.place.naver.com/place/1524946927</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4774,34 +4750,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>다대포 리핏1대1바디스쿨</t>
+          <t>듀오짐</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sondh44@naver.com</t>
+          <t>koreajongjoo@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1424-0777</t>
+          <t>0507-1379-1076</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 547 윤영빌딩 7층</t>
+          <t>부산광역시 사하구 낙동대로519번길 13 지하1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sondh44</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4831,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="Q47" t="n">
-        <v>165</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,47 +4822,51 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>33252149</t>
+          <t>1212394603</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33252149</t>
+          <t>https://m.place.naver.com/place/1212394603</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>준헬스피티</t>
+          <t>하단pt 더원짐</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>jlove518@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1411-0656</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 감천로 60-1</t>
+          <t>부산광역시 사하구 하신번영로 381-4 2층 더원짐</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jlove518</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4896,12 +4876,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4912,22 +4892,22 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R48" t="n">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,51 +4916,51 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1027715181</t>
+          <t>53386360</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027715181</t>
+          <t>https://m.place.naver.com/place/53386360</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네오피트니스 다대점</t>
+          <t>오늘필라테스 괴정점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lkz2995@naver.com</t>
+          <t>hyoj1nn_@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1424-8531</t>
+          <t>051-208-5005</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 613 자유마트상가 5층 502호 네오피트니스</t>
+          <t>부산광역시 사하구 낙동대로 218</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lkz2995</t>
+          <t>http://www.instagram.com/onl_pilates</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4995,7 +4975,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5015,13 +4995,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q49" t="n">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="R49" t="n">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5010,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1337361253</t>
+          <t>1943457137</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337361253</t>
+          <t>https://m.place.naver.com/place/1943457137</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5052,34 +5032,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1349-1867</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 534 6층</t>
+          <t>부산광역시 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wongym.kr</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5089,7 +5069,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5105,17 +5085,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>193</v>
+        <v>2077</v>
       </c>
       <c r="Q50" t="n">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="R50" t="n">
-        <v>436</v>
+        <v>2217</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,56 +5104,52 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1316442795</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1316442795</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>듀오짐</t>
+          <t>체인지바디스쿨</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>koreajongjoo@naver.com</t>
+          <t>ibs921@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1379-1076</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로519번길 13 지하1층</t>
+          <t>부산광역시 사하구 하신번영로 179 신평2동우체국건물 5층 체인지바디스쿨</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://blog.naver.com/ibs921</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5203,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="R51" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,47 +5194,51 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1212394603</t>
+          <t>1241403125</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1212394603</t>
+          <t>https://m.place.naver.com/place/1241403125</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>다대포헬스 &amp; PT 아이언짐 4호점</t>
+          <t>인더필라테스 &amp; 요가 괴정점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rlaruddjs1109@naver.com</t>
+          <t>inthepila@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1371-1120</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 473 맘모스상가 4층 아이언짐</t>
+          <t>부산광역시 사하구 사하로186번길 6 5,6층(괴정동, 하정빌딩)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/irongym_dadaepo_2</t>
+          <t>https://www.instagram.com/inthegym01</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5293,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="Q52" t="n">
-        <v>391</v>
+        <v>25</v>
       </c>
       <c r="R52" t="n">
-        <v>842</v>
+        <v>104</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5308,51 +5288,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1051347619</t>
+          <t>1314348239</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051347619</t>
+          <t>https://m.place.naver.com/place/1314348239</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>오늘필라테스 괴정점</t>
+          <t>트레이닝스튜디오 바름 본점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gjffod93@naver.com</t>
+          <t>yourim03070@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>051-208-5005</t>
+          <t>0507-1433-9887</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 218</t>
+          <t>부산광역시 사하구 다대로 381 도원 소아과3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/onl_pilates</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5362,7 +5342,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5383,17 +5363,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5402,51 +5382,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1943457137</t>
+          <t>905213182</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1943457137</t>
+          <t>https://m.place.naver.com/place/905213182</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피트니스 넘버원 헬스&amp;PT 괴정점</t>
+          <t>오앤오짐 장림</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>fitnessgymseung@naver.com</t>
+          <t>mmsy6242@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1388-7941</t>
+          <t>0507-1383-1354</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 203 엔스타상가 210,211호</t>
+          <t>부산광역시 사하구 하신중앙로 21 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/me/gymseung</t>
+          <t>https://www.instagram.com/ono_pt_grit</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5472,7 +5452,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5481,13 +5461,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="Q54" t="n">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="R54" t="n">
-        <v>314</v>
+        <v>57</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5496,17 +5476,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1519532322</t>
+          <t>1355627213</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519532322</t>
+          <t>https://m.place.naver.com/place/1355627213</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5498,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>더케이피트니스 롯데마트사하</t>
+          <t>원짐 하단 PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>thekfitness@naver.com</t>
+          <t>kht8kht@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1334-1844</t>
+          <t>0507-1349-1867</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 을숙도대로 610 롯데마트 사하점 4층</t>
+          <t>부산광역시 사하구 낙동대로 534 6층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.k_fitness_saha</t>
+          <t>https://www.instagram.com/wongym.kr</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5575,13 +5555,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="Q55" t="n">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="R55" t="n">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5590,17 +5570,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1183759558</t>
+          <t>1316442795</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183759558</t>
+          <t>https://m.place.naver.com/place/1316442795</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5612,24 +5592,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>스마트짐 다대포점</t>
+          <t>써밋퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>suk3084308@naver.com</t>
+          <t>jjuyaa_a@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1345-9679</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대낙조2길 85 케이프포인트 지하1층</t>
+          <t>부산광역시 사하구 제석로 160 당리동1차 동원베네스트 아파트 상가</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5669,13 +5645,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="R56" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,47 +5660,51 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1563027724</t>
+          <t>1515008554</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563027724</t>
+          <t>https://m.place.naver.com/place/1515008554</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>체인지바디스쿨</t>
+          <t>워너짐헬스&amp;PT 하단2지점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ibs921@naver.com</t>
+          <t>wannagym87@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1413-8976</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 179 신평2동우체국건물 5층 체인지바디스쿨</t>
+          <t>부산광역시 사하구 하신중앙로 299 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ibs921</t>
+          <t>https://blog.naver.com/wannagym87/223954977011</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5759,13 +5739,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="R57" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5774,17 +5754,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1241403125</t>
+          <t>1154806768</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241403125</t>
+          <t>https://m.place.naver.com/place/1154806768</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5796,29 +5776,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아이콘휘트니스</t>
+          <t>스마트짐 다대포점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>spain0805@naver.com</t>
+          <t>suk3084308@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>051-206-9996</t>
+          <t>0507-1345-9679</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1422 청경빌딩 6층 아이콘 휘트니스</t>
+          <t>부산광역시 사하구 다대낙조2길 85 케이프포인트 지하1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/icon_busan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5828,7 +5808,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5849,17 +5829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q58" t="n">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="R58" t="n">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5868,47 +5848,51 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37379330</t>
+          <t>1563027724</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37379330</t>
+          <t>https://m.place.naver.com/place/1563027724</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>점핑홀릭</t>
+          <t>올짐 피트니스 &amp; 사우나 대티점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>llbonobono@naver.com</t>
+          <t>allgym_daeti@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1384-8306</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 441 3층</t>
+          <t>부산광역시 사하구 낙동대로 137 대티역 스마트W 상가 1층 올짐 휘트니스 &amp; 사우나</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/allgym_daeti</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5918,12 +5902,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5939,17 +5923,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>748</v>
       </c>
       <c r="R59" t="n">
-        <v>11</v>
+        <v>1044</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5958,17 +5942,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1051113737</t>
+          <t>1698150913</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051113737</t>
+          <t>https://m.place.naver.com/place/1698150913</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5980,29 +5964,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>플러스짐 / 플러스휘트니스 헬스&amp;PT 다대포점</t>
+          <t>워너짐 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>plusfitnessdadae@naver.com</t>
+          <t>wannagym87@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1384-8809</t>
+          <t>0507-1477-1511</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대낙조2길 3 2층 201호</t>
+          <t>부산광역시 사하구 하신번영로 352 우리마트 2층(하단동)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/plusfitnessdadae</t>
+          <t>https://www.instagram.com/wannagym11_hadan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6017,7 +6001,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6033,17 +6017,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>64</v>
+        <v>399</v>
       </c>
       <c r="Q60" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="R60" t="n">
-        <v>148</v>
+        <v>450</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6052,17 +6036,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1260784487</t>
+          <t>1180864218</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260784487</t>
+          <t>https://m.place.naver.com/place/1180864218</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6074,29 +6058,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>휘트니스베이직</t>
+          <t>머슬팩토리 신평점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ryounghwa@naver.com</t>
+          <t>musclefactory_@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>051-204-5556</t>
+          <t>0507-1364-8147</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 184 동은빌딩 4층</t>
+          <t>부산광역시 사하구 하신중앙로 176 5층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/swxfwIHe</t>
+          <t>https://blog.naver.com/musclefactory_</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6111,7 +6095,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6122,7 +6106,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6131,13 +6115,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="Q61" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="R61" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6146,17 +6130,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>36448996</t>
+          <t>1102814447</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36448996</t>
+          <t>https://m.place.naver.com/place/1102814447</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6168,34 +6152,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GYM 루소킹 괴정점 헬스&amp;PT</t>
+          <t>에이토탈피트니스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gym_rusoking@naver.com</t>
+          <t>sinby1987@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1368-4733</t>
+          <t>0507-1433-0551</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로216번길 3 신화프라자 1층 괴정역2번출구 도보30초</t>
+          <t>부산광역시 사하구 사하로 182 아델하임 3층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_UxdxbUG/friend</t>
+          <t>https://blog.naver.com/sinby1987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6205,7 +6189,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6216,22 +6200,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>488</v>
+        <v>138</v>
       </c>
       <c r="Q62" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="R62" t="n">
-        <v>909</v>
+        <v>563</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6240,17 +6224,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37438088</t>
+          <t>1164084833</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438088</t>
+          <t>https://m.place.naver.com/place/1164084833</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6262,25 +6246,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>레드핏 퍼스널트레이닝 스튜디오</t>
+          <t>온유어짐PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>baby3258@naver.com</t>
+          <t>cksah99@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1354-4205</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 393 사하구청 건너편 버스정류소</t>
+          <t>부산광역시 사하구 다대동 1628 주상가 4층 407호 온유어짐</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baby3258</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6290,12 +6278,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6315,13 +6303,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6330,17 +6318,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>33907135</t>
+          <t>1770796114</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33907135</t>
+          <t>https://m.place.naver.com/place/1770796114</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6352,29 +6340,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>그린피트니스</t>
+          <t>위더스짐</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hcy1507@naver.com</t>
+          <t>with_us_1225@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>051-208-0551</t>
+          <t>0507-1303-4471</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로201번길 20 3층4층</t>
+          <t>부산광역시 사하구 낙동대로 519 지하 1층 위더스짐</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2019__gf</t>
+          <t>https://blog.naver.com/with_us_1225</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6389,7 +6377,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6409,13 +6397,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="R64" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6424,17 +6412,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1088337947</t>
+          <t>1081043765</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088337947</t>
+          <t>https://m.place.naver.com/place/1081043765</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6446,29 +6434,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>곤코치피트니스</t>
+          <t>다대포 헬스장&amp;PT 아이언짐 3호점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>groupcircuit@naver.com</t>
+          <t>irongymdadae@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1348-7871</t>
+          <t>051-263-0060</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 524 지하층</t>
+          <t>부산광역시 사하구 다송로 71 세인트마린 3층 아이언짐</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/groupcircuit</t>
+          <t>https://blog.naver.com/irongymdadae/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6499,17 +6487,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>17</v>
+        <v>253</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>451</v>
       </c>
       <c r="R65" t="n">
-        <v>27</v>
+        <v>704</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6518,47 +6506,51 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1173727453</t>
+          <t>1760440292</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1173727453</t>
+          <t>https://m.place.naver.com/place/1760440292</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>허그짐 다대포 낫개점 헬스&amp;PT</t>
+          <t>림필라테스&amp;PT스튜디오</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>huggymdadaepo9704@naver.com</t>
+          <t>lipblossom@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1419-8402</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다송로84번길 52 2, 3층</t>
+          <t>부산광역시 사하구 하신중앙로313번길 54 3층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huggymdadaepo9704</t>
+          <t>https://www.instagram.com/rimpilates_pt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6573,7 +6565,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6593,13 +6585,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>385</v>
+        <v>33</v>
       </c>
       <c r="Q66" t="n">
-        <v>346</v>
+        <v>14</v>
       </c>
       <c r="R66" t="n">
-        <v>731</v>
+        <v>47</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,51 +6600,51 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1095357843</t>
+          <t>1704290562</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095357843</t>
+          <t>https://m.place.naver.com/place/1704290562</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>요가인</t>
+          <t>레드 피트니스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bypoleon@naver.com</t>
+          <t>moonsi870@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>051-205-3114</t>
+          <t>0507-1354-0550</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 267 신동양상가 3층</t>
+          <t>부산광역시 사하구 제석로 89 3층, 4층 레드피트니스</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/red_fitness25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6662,7 +6654,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6683,17 +6675,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="Q67" t="n">
-        <v>100</v>
+        <v>314</v>
       </c>
       <c r="R67" t="n">
-        <v>109</v>
+        <v>380</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,17 +6694,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1258904158</t>
+          <t>1003594161</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258904158</t>
+          <t>https://m.place.naver.com/place/1003594161</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6724,44 +6716,44 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>하파휘트니스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>kdh31307o@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>051-293-3000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 440 5층</t>
+          <t>부산광역시 사하구 낙동대로 474 대하빌딩 7층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6781,13 +6773,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2075</v>
+        <v>302</v>
       </c>
       <c r="Q68" t="n">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="R68" t="n">
-        <v>2211</v>
+        <v>334</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,56 +6788,56 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>36771036</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/36771036</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>매료피티</t>
+          <t>스마트w 사우나&amp;휘트니스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>no1jin2@naver.com</t>
+          <t>wfitness3@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1396-4885</t>
+          <t>0507-1363-0214</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 승학로 19 4층</t>
+          <t>부산광역시 사하구 장림번영로104번길 10 지하1층 W사우나&amp;휘트니스</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maeryo_official777</t>
+          <t>https://blog.naver.com/wfitness3</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6855,7 +6847,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6871,17 +6863,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>299</v>
+        <v>50</v>
       </c>
       <c r="R69" t="n">
-        <v>410</v>
+        <v>50</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,17 +6882,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1438184043</t>
+          <t>1038609556</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438184043</t>
+          <t>https://m.place.naver.com/place/1038609556</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6912,30 +6904,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>천지연헬스</t>
+          <t>GYM 루소킹 괴정점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>c-jiyun@naver.com</t>
+          <t>gym_rusoking@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1368-4733</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로227번길 48</t>
+          <t>부산광역시 사하구 낙동대로216번길 3 신화프라자 1층 괴정역2번출구 도보30초</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/c-jiyun</t>
+          <t>http://pf.kakao.com/_UxdxbUG/friend</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6945,7 +6941,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6956,7 +6952,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6965,13 +6961,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>421</v>
       </c>
       <c r="R70" t="n">
-        <v>11</v>
+        <v>912</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,17 +6976,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1879711816</t>
+          <t>37438088</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1879711816</t>
+          <t>https://m.place.naver.com/place/37438088</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7002,29 +6998,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>힙터짐</t>
+          <t>최귀성프로짐</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sojamy@naver.com</t>
+          <t>umsoso@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1410-7420</t>
+          <t>0507-1375-4667</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 403 3층</t>
+          <t>부산광역시 사하구 다대로 299 3층 최귀성프로짐</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/trainer_dr.m</t>
+          <t>https://blog.naver.com/umsoso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7039,7 +7035,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7059,13 +7055,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="Q71" t="n">
-        <v>402</v>
+        <v>168</v>
       </c>
       <c r="R71" t="n">
-        <v>588</v>
+        <v>369</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,51 +7070,51 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>169586671</t>
+          <t>1650411626</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/169586671</t>
+          <t>https://m.place.naver.com/place/1650411626</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>스카이PT</t>
+          <t>리얼바디 기구필라테스&amp;PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>deok51@naver.com</t>
+          <t>realbodypt@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1300-6238</t>
+          <t>051-992-5252</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대낙조1길 19 성호빌딩 6층</t>
+          <t>부산광역시 사하구 다송로72번길 55 동양빌딩 5층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/deok51</t>
+          <t>https://www.instagram.com/realbody_pilates</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7133,7 +7129,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7149,17 +7145,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="Q72" t="n">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="R72" t="n">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1953925821</t>
+          <t>38530720</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953925821</t>
+          <t>https://m.place.naver.com/place/38530720</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7190,29 +7186,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>머슬팩토리 헬스&amp;PT 하단점</t>
+          <t>GO피트니스&amp;대기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>musclefactory_hadan@naver.com</t>
+          <t>gofitness_gj@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1372-0206</t>
+          <t>0507-1402-0240</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로201번길 10 지하1층</t>
+          <t>부산광역시 사하구 사하로 200 형지스퀘어 빌딩 7층, 8층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclefactory_hadan</t>
+          <t>https://www.instagram.com/gofit_goejeong/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7227,7 +7223,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7238,7 +7234,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7247,13 +7243,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>56</v>
+        <v>241</v>
       </c>
       <c r="Q73" t="n">
-        <v>203</v>
+        <v>457</v>
       </c>
       <c r="R73" t="n">
-        <v>259</v>
+        <v>698</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7262,51 +7258,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1846192246</t>
+          <t>31681303</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846192246</t>
+          <t>https://m.place.naver.com/place/31681303</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>코치엔짐</t>
+          <t>매료피티</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>iron0377@naver.com</t>
+          <t>no1jin2@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1386-9682</t>
+          <t>0507-1396-4885</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다송로72번길 80 라브랜드 4층</t>
+          <t>부산광역시 사하구 승학로 19 4층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iron0377</t>
+          <t>https://www.instagram.com/maeryo_official777</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7321,7 +7317,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7341,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>545</v>
+        <v>108</v>
       </c>
       <c r="Q74" t="n">
-        <v>198</v>
+        <v>300</v>
       </c>
       <c r="R74" t="n">
-        <v>743</v>
+        <v>408</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7356,56 +7352,56 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1524946927</t>
+          <t>1438184043</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1524946927</t>
+          <t>https://m.place.naver.com/place/1438184043</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>갓바디휘트니스 당리점</t>
+          <t>메이크핏</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>tjdgns3591@naver.com</t>
+          <t>make___fit@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1329-3591</t>
+          <t>0507-1309-2919</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 410 지하1층</t>
+          <t>부산광역시 사하구 하신번영로 239 2층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sDJqNLIh</t>
+          <t>https://blog.naver.com/make___fit</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7415,7 +7411,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7426,22 +7422,22 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="R75" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,17 +7446,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1003392887</t>
+          <t>1364930930</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003392887</t>
+          <t>https://m.place.naver.com/place/1364930930</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7472,29 +7468,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>온유어짐</t>
+          <t>프라이빗GYM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>cksah99@naver.com</t>
+          <t>privategym2014@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1354-4205</t>
+          <t>051-203-3190</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대동 1628 주상가 4층 407호 온유어짐</t>
+          <t>부산광역시 사하구 낙동대로 388 경성리치W상가 3층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/privategym2014</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7504,12 +7500,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7525,17 +7521,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R76" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7544,51 +7540,51 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1770796114</t>
+          <t>36132952</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1770796114</t>
+          <t>https://m.place.naver.com/place/36132952</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>워너짐 헬스&amp;PT 하단점</t>
+          <t>클리어짐</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>wannagym87@naver.com</t>
+          <t>clear_gym@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1477-1511</t>
+          <t>0507-1352-4221</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 352 우리마트 2층(하단동)</t>
+          <t>부산광역시 사하구 낙동대로233번길 21-17</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wannagym11_hadan</t>
+          <t>https://blog.naver.com/clear_gym</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7603,7 +7599,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7623,13 +7619,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>395</v>
+        <v>70</v>
       </c>
       <c r="Q77" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="R77" t="n">
-        <v>446</v>
+        <v>173</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7638,51 +7634,51 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1180864218</t>
+          <t>1545911961</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1180864218</t>
+          <t>https://m.place.naver.com/place/1545911961</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EMS트레이닝</t>
+          <t>폴인기구필라테스&amp;웨이트PT 부산 하단점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>emskoreasje@naver.com</t>
+          <t>fallin__22@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>051-204-9901</t>
+          <t>0507-1423-8311</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 385 SM빌딩 3층</t>
+          <t>부산광역시 사하구 낙동대로516번길 56 캠퍼스프라자2층 204호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fallin__22</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7692,12 +7688,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7713,17 +7709,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>496</v>
       </c>
       <c r="R78" t="n">
-        <v>15</v>
+        <v>637</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7732,17 +7728,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>36929012</t>
+          <t>548118354</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36929012</t>
+          <t>https://m.place.naver.com/place/548118354</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7754,25 +7750,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>피지오컨디셔닝운동센터</t>
+          <t>제로핏 PT 당리점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>move_tai@naver.com</t>
+          <t>zerofitpt@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1394-9604</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 137 103동 2층 피지오컨디셔닝운동센터</t>
+          <t>부산광역시 사하구 낙동대로 366 2층 제로핏</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://youtube.com/@피지오클럽</t>
+          <t>https://blog.naver.com/zerofitpt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="Q79" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="R79" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7822,17 +7822,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1452522646</t>
+          <t>1475333246</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452522646</t>
+          <t>https://m.place.naver.com/place/1475333246</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7844,29 +7844,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>오케이피트니스 다대포점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>okfitness_dadaepo@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1342-9583</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
+          <t>부산광역시 사하구 다대낙조1길 5 . 3,4층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://www.okfitness.co.kr</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7892,7 +7892,7 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7901,13 +7901,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1156</v>
+        <v>157</v>
       </c>
       <c r="Q80" t="n">
-        <v>421</v>
+        <v>168</v>
       </c>
       <c r="R80" t="n">
-        <v>1577</v>
+        <v>325</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7916,17 +7916,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1999206798</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1999206798</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7938,29 +7938,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>석파동주체육관</t>
+          <t>동아기능성운동트레이닝센터</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>gymbhu@naver.com</t>
+          <t>dfet0226@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>051-200-3434</t>
+          <t>0507-1494-7910</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사리로55번길 16 부산보건대학교 3층 석파동주체육관</t>
+          <t>부산광역시 사하구 낙동대로550번길 37 예술체육대학1관 106호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bhu_gym_?igsh=ZnlrMTZrNHpqMDVu&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/dfet0226</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7986,7 +7986,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7995,13 +7995,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="Q81" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="R81" t="n">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8010,51 +8010,51 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1723355388</t>
+          <t>1619665911</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1723355388</t>
+          <t>https://m.place.naver.com/place/1619665911</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
+          <t>지음 필라테스&amp;PT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>inthegym01@naver.com</t>
+          <t>jieumpilates@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1358-6699</t>
+          <t>0507-1423-7719</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
+          <t>부산광역시 사하구 다대로 630 4층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/inthegym01</t>
+          <t>https://www.instagram.com/jieum_pilates</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>591</v>
+        <v>93</v>
       </c>
       <c r="Q82" t="n">
-        <v>712</v>
+        <v>48</v>
       </c>
       <c r="R82" t="n">
-        <v>1303</v>
+        <v>141</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8104,51 +8104,51 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1419272513</t>
+          <t>1782696469</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419272513</t>
+          <t>https://m.place.naver.com/place/1782696469</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>제로핏 PT 당리점</t>
+          <t>스핀업스피닝</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>zerofitpt@naver.com</t>
+          <t>kej6254@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1394-9604</t>
+          <t>0507-1400-2070</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 366 2층 제로핏</t>
+          <t>부산광역시 사하구 낙동대로 548</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zerofitpt</t>
+          <t>http://cafe.naver.com/spinupspining</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8198,17 +8198,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1475333246</t>
+          <t>37333233</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1475333246</t>
+          <t>https://m.place.naver.com/place/37333233</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8220,29 +8220,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>머슬팩토리 신평점</t>
+          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>musclefactory_@naver.com</t>
+          <t>jlfitness_j@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1364-8147</t>
+          <t>0507-1310-1470</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신중앙로 176 5층</t>
+          <t>부산광역시 사하구 장림번영로 50 상가 2층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclefactory_</t>
+          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8277,13 +8277,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>56</v>
+        <v>1220</v>
       </c>
       <c r="Q84" t="n">
-        <v>43</v>
+        <v>622</v>
       </c>
       <c r="R84" t="n">
-        <v>99</v>
+        <v>1842</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1102814447</t>
+          <t>1315960121</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102814447</t>
+          <t>https://m.place.naver.com/place/1315960121</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8314,29 +8314,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>괴정메가스포츠센터&amp;PT</t>
+          <t>짐크래커 부산점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>bbvn1539@naver.com</t>
+          <t>gymcracker1517@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>051-207-7744</t>
+          <t>051-293-8788</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 261 자유상가 지하1층</t>
+          <t>부산광역시 사하구 하신번영로 365 가락타운1단지 145동 상가 3F</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bbvn1539</t>
+          <t>https://blog.naver.com/gymcracker1517</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8367,17 +8367,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="R85" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8386,17 +8386,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>16619186</t>
+          <t>1213321291</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16619186</t>
+          <t>https://m.place.naver.com/place/1213321291</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8408,29 +8408,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;PT 하단점</t>
+          <t>디파인짐 구평점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>404fitnesshadan@naver.com</t>
+          <t>thefinegym_gp@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1395-4026</t>
+          <t>0507-1433-7073</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 487 4층</t>
+          <t>부산광역시 사하구 서포로30번길 3 3층 301,302호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/404_fitness_hadan/</t>
+          <t>https://www.instagram.com/thefinegym</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>403</v>
+        <v>30</v>
       </c>
       <c r="Q86" t="n">
-        <v>278</v>
+        <v>92</v>
       </c>
       <c r="R86" t="n">
-        <v>681</v>
+        <v>122</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8480,51 +8480,47 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1669341529</t>
+          <t>1008480964</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669341529</t>
+          <t>https://m.place.naver.com/place/1008480964</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>핏튜브짐 &amp; 필라테스</t>
+          <t>천지연헬스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>boong_see@naver.com</t>
+          <t>c-jiyun@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0507-1465-5152</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 417 2층</t>
+          <t>부산광역시 사하구 다대로227번길 48</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/c-jiyun</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8534,12 +8530,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8559,13 +8555,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q87" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8574,51 +8570,47 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1226166767</t>
+          <t>1879711816</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226166767</t>
+          <t>https://m.place.naver.com/place/1879711816</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>에이토탈피트니스</t>
+          <t>비앤에스짐</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sinby1987@naver.com</t>
+          <t>bsboxing1171@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1433-0551</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로 182 아델하임 3층</t>
+          <t>부산광역시 사하구 하신중앙로 2 301호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sinby1987</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8628,12 +8620,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8649,17 +8641,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8668,51 +8660,51 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1164084833</t>
+          <t>2033918601</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164084833</t>
+          <t>https://m.place.naver.com/place/2033918601</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>다대포 헬스장&amp;PT 아이언짐 3호점</t>
+          <t>석파동주체육관</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>irongymdadae@naver.com</t>
+          <t>gymbhu@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>051-263-0060</t>
+          <t>051-200-3434</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다송로 71 세인트마린 3층 아이언짐</t>
+          <t>부산광역시 사하구 사리로55번길 16 부산보건대학교 3층 석파동주체육관</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/irongymdadae/</t>
+          <t>https://www.instagram.com/bhu_gym_?igsh=ZnlrMTZrNHpqMDVu&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8727,7 +8719,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8738,7 +8730,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8747,13 +8739,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>253</v>
+        <v>54</v>
       </c>
       <c r="Q89" t="n">
-        <v>453</v>
+        <v>33</v>
       </c>
       <c r="R89" t="n">
-        <v>706</v>
+        <v>87</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8762,17 +8754,111 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1760440292</t>
+          <t>1723355388</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760440292</t>
+          <t>https://m.place.naver.com/place/1723355388</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>힙터짐</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sojamy@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1410-7420</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>부산광역시 사하구 낙동대로 403 3층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trainer_dr.m</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>402</v>
+      </c>
+      <c r="R90" t="n">
+        <v>589</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>169586671</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/169586671</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
